--- a/Organization_Template_Alternate.xlsx
+++ b/Organization_Template_Alternate.xlsx
@@ -16,8 +16,7 @@
     <sheet name="Contact people" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Notes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Accounts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -776,36 +775,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.140625" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Organization_Template_Alternate.xlsx
+++ b/Organization_Template_Alternate.xlsx
@@ -163,7 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -224,6 +224,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,7 +656,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. One exception: an interface's USERNAME/PASSWORD (on the Interfaces sheet) aren't colored as mandatory since an interface doesn't need login credentials at all - but if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally).</t>
+          <t>This applies on every sheet, not just Main Org record - e.g. PHONE on the Phones sheet, EMAIL on the Emails sheet, ACCOUNT NAME/ACCOUNT NUMBER/ACCOUNT STATUS on the Accounts sheet. A colored column can also be a 'required if you use this at all' pair rather than a plain single field: an interface's USERNAME/PASSWORD (on the Interfaces sheet) are both colored because if you fill in either one, you must fill in both, or just that login-credentials record is skipped (the interface itself, and the rest of that organization, still build normally). The Interfaces sheet's own NAME column, on the other hand, is intentionally NOT colored - the real FOLIO interface record has no required fields of its own, not even a name.</t>
         </is>
       </c>
     </row>
@@ -915,6 +918,7 @@
     <col width="11.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="16.140625" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="35" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -960,7 +964,11 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="28" t="inlineStr">
+        <is>
+          <t>ORG TYPE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -1081,7 +1089,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="I1" s="28" t="inlineStr">
@@ -1133,7 +1141,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
@@ -1225,7 +1233,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
@@ -1274,13 +1282,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.140625" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1302,10 +1310,15 @@
       </c>
       <c r="D1" s="28" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+      <c r="F1" s="28" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
@@ -1367,12 +1380,12 @@
           <t>NOTES</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
@@ -1384,7 +1397,7 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>CATEGORY</t>
+          <t>CATEGORIES</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1498,7 @@
           <t>ORG CODE</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
@@ -1505,12 +1518,12 @@
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="31" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="31" t="inlineStr">
         <is>
           <t>PASSWORD</t>
         </is>

--- a/Organization_Template_Alternate.xlsx
+++ b/Organization_Template_Alternate.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Interfaces" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor info" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Accounts" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -903,6 +904,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.57" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>ORG CODE</t>
+        </is>
+      </c>
+      <c r="B1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TYPE</t>
+        </is>
+      </c>
+      <c r="C1" s="31" t="inlineStr">
+        <is>
+          <t>NOTE TITLE</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>CONTENTS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1340,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1372,30 +1415,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TITLE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>NOTES</t>
         </is>
       </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>EMAIL</t>
+        </is>
+      </c>
       <c r="F1" s="32" t="inlineStr">
         <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="G1" s="32" t="inlineStr">
-        <is>
           <t xml:space="preserve">PHONE </t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
@@ -1418,18 +1456,17 @@
         </is>
       </c>
       <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>jnovak@ebsco.com</t>
+        </is>
+      </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>jnovak@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
           <t>555-555-5555</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Accounts receivable</t>
         </is>
@@ -1452,18 +1489,17 @@
         </is>
       </c>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>mrossi@ebsco.com</t>
+        </is>
+      </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>mrossi@ebsco.com</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
           <t>555-555-5555</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Customer service</t>
         </is>

--- a/Organization_Template_Alternate.xlsx
+++ b/Organization_Template_Alternate.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-37452" yWindow="10548" windowWidth="21744" windowHeight="11844" tabRatio="731" firstSheet="8" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1650" yWindow="1455" windowWidth="25050" windowHeight="13140" tabRatio="731" firstSheet="1" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="How to use this workbook" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,14 +20,14 @@
     <sheet name="External note" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,22 +90,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <charset val="1"/>
-      <color theme="1"/>
-      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
-      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Source Sans Pro"/>
-      <i val="1"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -164,7 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -177,39 +174,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
@@ -218,16 +192,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,7 +597,7 @@
   <dimension ref="B2:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.140625" customWidth="1" min="2" max="2"/>
+    <col width="12.140625" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -641,14 +629,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Go to Main Org record sheet</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Please note that coloured columns are mandatory.</t>
         </is>
@@ -689,86 +677,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.42578125" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="14"/>
+    <col width="14.42578125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="15" customWidth="1" style="24" min="2" max="10"/>
+    <col width="15" customWidth="1" style="12" min="11" max="11"/>
+    <col width="15" customWidth="1" style="24" min="12" max="13"/>
+    <col width="15" customWidth="1" style="12" min="14" max="14"/>
+    <col width="11.42578125" bestFit="1" customWidth="1" style="24" min="26" max="26"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
+    <row r="1" ht="60" customHeight="1" s="24">
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Pipe delimited (|) list of currencies permitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="C1" s="27" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>CURRENCIES</t>
         </is>
       </c>
-      <c r="D1" s="27" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>CLAIMING INTERVAL</t>
         </is>
       </c>
-      <c r="E1" s="27" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>DISCOUNT %</t>
         </is>
       </c>
-      <c r="F1" s="27" t="inlineStr">
-        <is>
-          <t>EXP ACTIVATION INTERVAL</t>
-        </is>
-      </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>EXPECTED ACTIVATION INTERVAL</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>EXP INVOICE INTERVAL</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>EXP RECEIPT INTERVAL</t>
         </is>
       </c>
-      <c r="I1" s="27" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>RENEWAL ACTIVATION INTERVAL</t>
         </is>
       </c>
-      <c r="J1" s="27" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>SUBSCRIPTION INTERVAL</t>
         </is>
       </c>
-      <c r="K1" s="27" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>EXPORT TO ACCOUNTING (Y/)</t>
         </is>
       </c>
-      <c r="L1" s="27" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>TAX ID</t>
         </is>
       </c>
-      <c r="M1" s="27" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>TAX %</t>
         </is>
       </c>
-      <c r="N1" s="27" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>LIABLE FOR VAT (Y/N)</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Do not edit:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="K3:K1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>$AA$2:$AA$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -779,127 +798,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A2:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.28515625" customWidth="1" style="20" min="1" max="1"/>
-    <col width="22.140625" customWidth="1" min="2" max="2"/>
-    <col width="20.85546875" customWidth="1" min="3" max="3"/>
-    <col width="36.5703125" customWidth="1" min="4" max="4"/>
-    <col width="24.5703125" customWidth="1" min="5" max="6"/>
-    <col width="25.85546875" customWidth="1" min="7" max="7"/>
-    <col width="18.85546875" customWidth="1" style="15" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13.28515625" customWidth="1" style="23" min="1" max="1"/>
+    <col width="22.140625" customWidth="1" style="24" min="2" max="2"/>
+    <col width="20.85546875" customWidth="1" style="24" min="3" max="3"/>
+    <col width="36.5703125" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24.5703125" customWidth="1" style="24" min="5" max="6"/>
+    <col width="25.85546875" customWidth="1" style="24" min="7" max="7"/>
+    <col width="18.85546875" customWidth="1" style="8" min="8" max="8"/>
+    <col width="20" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="24">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="22" t="inlineStr">
-        <is>
-          <t>ACCOUNT NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="30" t="inlineStr">
-        <is>
-          <t>ACCOUNT NUMBER</t>
-        </is>
-      </c>
-      <c r="D1" s="23" t="inlineStr">
+    <row r="2" customFormat="1" s="10">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>ACCOUNT NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>ACCOUNT NUMBER*</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>ACCOUNTING CODE</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>PAYMENT METHOD</t>
         </is>
       </c>
-      <c r="G1" s="30" t="inlineStr">
-        <is>
-          <t>ACCOUNT STATUS</t>
-        </is>
-      </c>
-      <c r="H1" s="26" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
+        <is>
+          <t>ACCOUNT STATUS*</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>LIBRARY EDI CODE</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO eBooks</t>
-        </is>
-      </c>
-      <c r="C2" s="25" t="n">
-        <v>12345</v>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>ebooks purchased from EBSCO</t>
-        </is>
-      </c>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H2" s="25" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO databases</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="n">
-        <v>12346</v>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>databases purchased from EBSCO</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="H3" s="25" t="n">
-        <v>456</v>
-      </c>
-    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="G3:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Active,Inactive,Pending"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -910,32 +874,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A2:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.57" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="10.5703125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="15" customWidth="1" style="24" min="2" max="2"/>
+    <col width="30" customWidth="1" style="24" min="3" max="3"/>
+    <col width="50" customWidth="1" style="24" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="31" t="inlineStr">
-        <is>
-          <t>NOTE TYPE</t>
-        </is>
-      </c>
-      <c r="C1" s="31" t="inlineStr">
-        <is>
-          <t>NOTE TITLE</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>NOTE TYPE*</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>NOTE TITLE*</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>CONTENTS</t>
         </is>
@@ -956,40 +920,40 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11.42578125" customWidth="1" style="8" min="1" max="1"/>
-    <col width="25.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="16.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="35" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="11.42578125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="25.42578125" customWidth="1" style="24" min="2" max="2"/>
+    <col width="16.140625" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="36" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
+    <col width="35" bestFit="1" customWidth="1" style="24" min="5" max="5"/>
+    <col width="40" bestFit="1" customWidth="1" style="24" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="B1" s="12" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1" s="24">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>NOTE: Unlike the original Organization_Template.xlsx, this sheet holds only the fields that can't repeat. Every address, phone number, email, URL, and alternative name for this organization - including the first one - belongs on the Addresses/Phones/Emails/URLs/Alt names sheet instead.</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="B2" s="12" t="n"/>
+    <row r="2" ht="18.75" customHeight="1" s="24">
+      <c r="B2" s="14" t="n"/>
     </row>
     <row r="3">
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Coloured columns are mandatory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>ORG NAME</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Columns marked with * are mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="24">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>ORG NAME*</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -997,9 +961,9 @@
           <t>Vendor (Yes/No)</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>ORG status (Active/Inactive/Pending)</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ORG status (Active/Inactive/Pending)*</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1007,35 +971,30 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
-        <is>
-          <t>ORG TYPE</t>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>ORG TYPE (Choose one or create your own)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>EBSCO Information Services</t>
-        </is>
-      </c>
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="15" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="10" t="n"/>
+      <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="7" ht="15.75" customHeight="1" s="24"/>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="C6:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
     <dataValidation sqref="D6:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Active, Inactive, Pending"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6:F1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"Access provider,Auction house,Book trade,Consortium,Content provider,Logistics,Material supplier,Membership organization,Private person,Publisher"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1049,26 +1008,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A2:C2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="7.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="15.42578125" customWidth="1" min="1" max="1"/>
-    <col width="11.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="13.28515625" customWidth="1" min="3" max="3"/>
+    <col width="15.42578125" customWidth="1" style="24" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" style="24" min="2" max="2"/>
+    <col width="13.28515625" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>ALT NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ALT NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1085,66 +1044,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A2:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20.28515625" customWidth="1" min="1" max="1"/>
-    <col width="13.28515625" customWidth="1" min="6" max="6"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20.28515625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="45.7109375" customWidth="1" style="24" min="2" max="3"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="13.28515625" customWidth="1" style="24" min="6" max="6"/>
+    <col width="14.5703125" customWidth="1" style="24" min="7" max="7"/>
+    <col width="19.42578125" customWidth="1" style="24" min="8" max="8"/>
+    <col width="14" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ADDR1 </t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>ADDR2</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>CITY</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>REGION</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>POSTAL CODE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>COUNTRY</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="I1" s="28" t="inlineStr">
+      <c r="I2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="I3:I1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1157,85 +1122,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A2:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16.7109375" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" style="8" min="2" max="2"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16.7109375" customWidth="1" style="24" min="1" max="1"/>
+    <col width="15" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PHONE*</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>800-653-2726</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n"/>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>800-633-4604</t>
-        </is>
-      </c>
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C3:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Office, Mobile, Fax, Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1248,71 +1190,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A2:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.140625" customWidth="1" min="1" max="1"/>
-    <col width="27.140625" customWidth="1" style="8" min="2" max="2"/>
-    <col width="27.140625" customWidth="1" min="3" max="3"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18.140625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="27.140625" customWidth="1" style="24" min="2" max="3"/>
+    <col width="11.140625" bestFit="1" customWidth="1" style="24" min="4" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>EMAIL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EMAIL*</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>customerservice@ebsco.com</t>
-        </is>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>sales@ebsco.com</t>
-        </is>
-      </c>
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1325,52 +1258,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A2:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.140625" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18.140625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="40" customWidth="1" style="24" min="2" max="2"/>
+    <col width="30" customWidth="1" style="24" min="3" max="4"/>
+    <col width="14" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="31" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>URL*</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-      <c r="F1" s="28" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>IS PRIMARY</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="E4:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Yes, No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1383,129 +1318,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A2:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="20.25" customHeight="1"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.140625" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.7109375" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
-    <col width="6.28515625" customWidth="1" min="4" max="4"/>
-    <col width="7.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="23.28515625" customWidth="1" style="8" min="6" max="6"/>
-    <col width="14.42578125" customWidth="1" style="8" min="7" max="7"/>
-    <col width="18.28515625" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
+    <col width="12.7109375" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="12.42578125" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24.85546875" customWidth="1" style="24" min="5" max="5"/>
+    <col width="23.28515625" customWidth="1" style="24" min="6" max="6"/>
+    <col width="14.42578125" customWidth="1" style="24" min="7" max="7"/>
+    <col width="18.28515625" customWidth="1" style="24" min="8" max="8"/>
+    <col width="13" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customFormat="1" customHeight="1" s="3">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>LAST NAME</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>FIRST NAME</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+    <row r="2" ht="20.25" customFormat="1" customHeight="1" s="3">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>LAST NAME*</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>FIRST NAME*</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="E1" s="32" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="F1" s="32" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">PHONE </t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>CATEGORIES</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Novak</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>jnovak@ebsco.com</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>555-555-5555</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Rossi</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Mario</t>
-        </is>
-      </c>
+      <c r="J2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="20.25" customHeight="1" s="24">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>mrossi@ebsco.com</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>555-555-5555</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>Customer service</t>
-        </is>
-      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="20.25" customHeight="1" s="24">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="H3:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Accounts Payable,Administrative,Claims and queries,Customer Service,Licensing,Payments,Receiving orders,Returns,Sales,Shipments,Support"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1516,119 +1409,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14.42578125" customWidth="1" style="8" min="2" max="2"/>
-    <col width="11.85546875" customWidth="1" min="3" max="3"/>
-    <col width="35.7109375" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="6"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="13.140625" customWidth="1" min="8" max="8"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="14.42578125" customWidth="1" style="24" min="2" max="2"/>
+    <col width="11.85546875" customWidth="1" style="24" min="3" max="3"/>
+    <col width="35.7109375" customWidth="1" style="24" min="4" max="4"/>
+    <col width="18" customWidth="1" style="24" min="5" max="6"/>
+    <col width="16.140625" customWidth="1" style="24" min="7" max="7"/>
+    <col width="13.140625" customWidth="1" style="24" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>ORG CODE</t>
-        </is>
-      </c>
-      <c r="B1" s="32" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="24">
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>If a username is present, a password must be set as well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="24">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>ORG CODE*</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>NAME</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TYPE</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>DELIVERY METHOD</t>
         </is>
       </c>
-      <c r="F1" s="31" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>USERNAME</t>
         </is>
       </c>
-      <c r="G1" s="31" t="inlineStr">
+      <c r="G2" s="25" t="inlineStr">
         <is>
           <t>PASSWORD</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>EBSCO Admin</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>https://eadmin.ebscohost.com/eadmin</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>myuser</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>mypass</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="n"/>
-    </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>E.g., ebsco</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>EBSCONET</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ebsconet.com</t>
-        </is>
-      </c>
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="D3" s="17" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C3:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Admin, End user, Reports, Orders, Invoices, Other"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E3:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Online, FTP, Email, Other"</formula1>
     </dataValidation>
   </dataValidations>
